--- a/events/Krakow_2024_WC/Krakow_2024_WC_start.xlsx
+++ b/events/Krakow_2024_WC/Krakow_2024_WC_start.xlsx
@@ -31458,6 +31458,11 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
